--- a/data/trans_dic/P25A$preocupacion-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25A$preocupacion-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 13,9</t>
+          <t>4,4; 13,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 14,13</t>
+          <t>5,49; 14,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 10,96</t>
+          <t>1,7; 10,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,17</t>
+          <t>0,0; 17,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 15,83</t>
+          <t>1,56; 16,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 13,55</t>
+          <t>1,59; 13,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 12,08</t>
+          <t>4,52; 12,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 12,69</t>
+          <t>5,61; 12,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 9,42</t>
+          <t>2,34; 9,24</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 10,85</t>
+          <t>3,35; 10,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 13,61</t>
+          <t>5,3; 13,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 23,6</t>
+          <t>11,66; 23,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 20,33</t>
+          <t>5,49; 20,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,46</t>
+          <t>1,05; 9,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 19,85</t>
+          <t>6,39; 19,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 12,46</t>
+          <t>5,0; 12,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 10,77</t>
+          <t>4,67; 10,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,31; 19,99</t>
+          <t>11,6; 21,41</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 16,79</t>
+          <t>5,73; 16,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,64</t>
+          <t>2,36; 9,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 17,39</t>
+          <t>6,58; 18,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 25,61</t>
+          <t>2,7; 23,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 16,11</t>
+          <t>4,34; 16,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 15,7</t>
+          <t>2,5; 17,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 15,36</t>
+          <t>6,14; 15,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 10,06</t>
+          <t>3,59; 9,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 14,7</t>
+          <t>5,92; 14,56</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 10,43</t>
+          <t>3,34; 10,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 11,67</t>
+          <t>4,32; 12,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 18,26</t>
+          <t>8,05; 18,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 12,62</t>
+          <t>2,15; 12,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 20,09</t>
+          <t>6,82; 20,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 13,6</t>
+          <t>3,64; 13,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,61</t>
+          <t>3,61; 9,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 13,01</t>
+          <t>6,62; 13,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 14,56</t>
+          <t>7,45; 14,57</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,94</t>
+          <t>5,66; 10,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 9,94</t>
+          <t>5,93; 9,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,35; 14,89</t>
+          <t>9,63; 14,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,65</t>
+          <t>4,89; 12,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 11,3</t>
+          <t>5,37; 11,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 11,36</t>
+          <t>5,47; 11,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,87</t>
+          <t>6,03; 9,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,77</t>
+          <t>6,35; 9,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 12,86</t>
+          <t>8,78; 12,93</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5720; 17985</t>
+          <t>5694; 17585</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9801; 26665</t>
+          <t>10360; 27775</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2050; 12956</t>
+          <t>2012; 12583</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7917</t>
+          <t>0; 7040</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1082; 11409</t>
+          <t>1125; 12109</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>854; 7290</t>
+          <t>854; 7489</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6751; 20626</t>
+          <t>7725; 21939</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13444; 33086</t>
+          <t>14623; 33782</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3902; 16203</t>
+          <t>4019; 15891</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6763; 20282</t>
+          <t>6250; 20457</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13544; 33847</t>
+          <t>13177; 34237</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19872; 41832</t>
+          <t>20661; 42050</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4078; 15638</t>
+          <t>4223; 15864</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1035; 9299</t>
+          <t>1032; 9229</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5567; 17135</t>
+          <t>5514; 17085</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13092; 32857</t>
+          <t>13190; 32025</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15813; 37382</t>
+          <t>16192; 37736</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29810; 52686</t>
+          <t>30570; 56442</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7837; 22549</t>
+          <t>7693; 22654</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3998; 16613</t>
+          <t>4065; 16112</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8042; 23217</t>
+          <t>8788; 24825</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1514; 10162</t>
+          <t>1071; 9199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4200; 16620</t>
+          <t>4478; 16978</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1838; 11709</t>
+          <t>1862; 12795</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10970; 26721</t>
+          <t>10676; 27643</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10005; 27707</t>
+          <t>9890; 26793</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12607; 30592</t>
+          <t>12324; 30298</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6126; 18139</t>
+          <t>5813; 17848</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9402; 24084</t>
+          <t>8908; 24864</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13677; 32227</t>
+          <t>14216; 32180</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2075; 11716</t>
+          <t>1999; 11223</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8012; 22697</t>
+          <t>7711; 23051</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4172; 16473</t>
+          <t>4413; 16108</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10174; 25639</t>
+          <t>9620; 25789</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20476; 41540</t>
+          <t>21140; 42847</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21563; 43315</t>
+          <t>22159; 43374</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36167; 62083</t>
+          <t>35340; 63240</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48967; 81135</t>
+          <t>48425; 80815</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56644; 90187</t>
+          <t>58291; 90426</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13204; 31723</t>
+          <t>12250; 30475</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21379; 43687</t>
+          <t>20743; 43260</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18524; 38153</t>
+          <t>18371; 38529</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53133; 86402</t>
+          <t>52820; 86850</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>76504; 117461</t>
+          <t>76378; 117202</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>83249; 121094</t>
+          <t>82691; 121724</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$preocupacion-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25A$preocupacion-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 13,59</t>
+          <t>4,4; 13,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 14,72</t>
+          <t>5,47; 14,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 10,64</t>
+          <t>1,8; 10,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,05</t>
+          <t>0,0; 18,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 16,8</t>
+          <t>1,58; 16,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 13,92</t>
+          <t>1,57; 14,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 12,85</t>
+          <t>4,54; 12,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 12,96</t>
+          <t>5,14; 12,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 9,24</t>
+          <t>2,24; 9,01</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 10,95</t>
+          <t>3,61; 11,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 13,77</t>
+          <t>5,32; 13,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 23,72</t>
+          <t>11,26; 23,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 20,62</t>
+          <t>5,44; 21,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,39</t>
+          <t>1,04; 7,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 19,79</t>
+          <t>6,4; 20,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 12,14</t>
+          <t>5,01; 11,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 10,87</t>
+          <t>4,45; 10,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,6; 21,41</t>
+          <t>10,91; 20,09</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 16,87</t>
+          <t>5,52; 16,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 9,35</t>
+          <t>2,39; 9,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 18,59</t>
+          <t>6,23; 17,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 23,18</t>
+          <t>2,5; 23,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,34; 16,46</t>
+          <t>4,46; 16,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 17,16</t>
+          <t>1,44; 16,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 15,89</t>
+          <t>6,03; 16,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 9,72</t>
+          <t>3,84; 10,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 14,56</t>
+          <t>6,16; 15,09</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,26</t>
+          <t>3,47; 10,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 12,05</t>
+          <t>4,6; 11,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 18,23</t>
+          <t>8,2; 18,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 12,09</t>
+          <t>2,08; 12,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 20,4</t>
+          <t>6,98; 20,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 13,3</t>
+          <t>3,61; 13,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,67</t>
+          <t>3,59; 9,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 13,42</t>
+          <t>6,38; 13,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 14,57</t>
+          <t>7,31; 14,3</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 10,13</t>
+          <t>5,79; 10,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,93; 9,9</t>
+          <t>5,88; 9,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,63; 14,93</t>
+          <t>9,32; 14,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,89; 12,15</t>
+          <t>5,27; 12,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,37; 11,19</t>
+          <t>5,51; 11,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 11,47</t>
+          <t>5,61; 11,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,92</t>
+          <t>6,11; 9,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,35; 9,75</t>
+          <t>6,39; 9,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,93</t>
+          <t>8,66; 12,71</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5694; 17585</t>
+          <t>5693; 17539</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10360; 27775</t>
+          <t>10312; 26824</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2012; 12583</t>
+          <t>2126; 12848</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7040</t>
+          <t>0; 7721</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1125; 12109</t>
+          <t>1142; 12238</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>854; 7489</t>
+          <t>845; 7649</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7725; 21939</t>
+          <t>7748; 21258</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14623; 33782</t>
+          <t>13395; 32596</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4019; 15891</t>
+          <t>3846; 15503</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6250; 20457</t>
+          <t>6751; 21257</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13177; 34237</t>
+          <t>13234; 33212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20661; 42050</t>
+          <t>19956; 40817</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4223; 15864</t>
+          <t>4184; 16644</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1032; 9229</t>
+          <t>1024; 7836</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5514; 17085</t>
+          <t>5529; 17912</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13190; 32025</t>
+          <t>13209; 31632</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16192; 37736</t>
+          <t>15437; 36766</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30570; 56442</t>
+          <t>28762; 52960</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7693; 22654</t>
+          <t>7408; 21576</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4065; 16112</t>
+          <t>4127; 15998</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8788; 24825</t>
+          <t>8319; 22715</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1071; 9199</t>
+          <t>993; 9365</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4478; 16978</t>
+          <t>4604; 16965</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1862; 12795</t>
+          <t>1076; 11942</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10676; 27643</t>
+          <t>10486; 27890</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9890; 26793</t>
+          <t>10571; 27657</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12324; 30298</t>
+          <t>12818; 31411</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5813; 17848</t>
+          <t>6033; 17989</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8908; 24864</t>
+          <t>9489; 23982</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14216; 32180</t>
+          <t>14465; 32161</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1999; 11223</t>
+          <t>1932; 11517</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7711; 23051</t>
+          <t>7887; 23136</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4413; 16108</t>
+          <t>4378; 16787</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9620; 25789</t>
+          <t>9576; 25219</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21140; 42847</t>
+          <t>20361; 41815</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22159; 43374</t>
+          <t>21758; 42562</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35340; 63240</t>
+          <t>36141; 63195</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48425; 80815</t>
+          <t>48021; 80630</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58291; 90426</t>
+          <t>56420; 89752</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12250; 30475</t>
+          <t>13218; 31847</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20743; 43260</t>
+          <t>21302; 45371</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18371; 38529</t>
+          <t>18835; 39684</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52820; 86850</t>
+          <t>53517; 85331</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>76378; 117202</t>
+          <t>76889; 116045</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>82691; 121724</t>
+          <t>81514; 119615</t>
         </is>
       </c>
     </row>
